--- a/data/trans_orig/P26-Clase-trans_orig.xlsx
+++ b/data/trans_orig/P26-Clase-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si tienen algún familiar que fuma habitualmente en casa en 2007</t>
+          <t>Población según si tienen algún familiar que fuma habitualmente en casa en 2007 (tasa de respuesta: 99,93%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>79791</t>
+          <t>79437</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>113978</t>
+          <t>115381</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>18,06%</t>
+          <t>17,98%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>25,79%</t>
+          <t>26,11%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>60904</t>
+          <t>62006</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>91986</t>
+          <t>91966</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>21,98%</t>
+          <t>22,38%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>33,2%</t>
+          <t>33,19%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>150836</t>
+          <t>149346</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>197860</t>
+          <t>195537</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>20,98%</t>
+          <t>20,77%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>27,52%</t>
+          <t>27,2%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>327942</t>
+          <t>326539</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>362129</t>
+          <t>362483</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>74,21%</t>
+          <t>73,89%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>81,94%</t>
+          <t>82,02%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>185093</t>
+          <t>185113</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>216175</t>
+          <t>215073</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>66,8%</t>
+          <t>66,81%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>78,02%</t>
+          <t>77,62%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>521139</t>
+          <t>523462</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>568163</t>
+          <t>569653</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>72,48%</t>
+          <t>72,8%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>79,02%</t>
+          <t>79,23%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>61057</t>
+          <t>60957</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>91850</t>
+          <t>92329</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>18,46%</t>
+          <t>18,43%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>27,77%</t>
+          <t>27,91%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>108947</t>
+          <t>109900</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>144421</t>
+          <t>145973</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>31,08%</t>
+          <t>31,35%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>41,19%</t>
+          <t>41,64%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>178540</t>
+          <t>177721</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>226091</t>
+          <t>227059</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>26,2%</t>
+          <t>26,08%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>33,18%</t>
+          <t>33,32%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>238920</t>
+          <t>238441</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>269713</t>
+          <t>269813</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>72,23%</t>
+          <t>72,09%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>81,54%</t>
+          <t>81,57%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>206166</t>
+          <t>204614</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>241640</t>
+          <t>240687</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>58,81%</t>
+          <t>58,36%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>68,92%</t>
+          <t>68,65%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>455267</t>
+          <t>454299</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>502818</t>
+          <t>503637</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>66,82%</t>
+          <t>66,68%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>73,8%</t>
+          <t>73,92%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>124088</t>
+          <t>126330</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>164724</t>
+          <t>165797</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>24,11%</t>
+          <t>24,55%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>32,01%</t>
+          <t>32,22%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>56147</t>
+          <t>56155</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>81335</t>
+          <t>80205</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1474,7 +1474,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>52,26%</t>
+          <t>51,53%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>189702</t>
+          <t>190741</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>237828</t>
+          <t>237120</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>28,3%</t>
+          <t>28,46%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>35,48%</t>
+          <t>35,38%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>349914</t>
+          <t>348841</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>390550</t>
+          <t>388308</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>67,99%</t>
+          <t>67,78%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>75,89%</t>
+          <t>75,45%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>74304</t>
+          <t>75434</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>99492</t>
+          <t>99484</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,7 +1582,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>47,74%</t>
+          <t>48,47%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>432448</t>
+          <t>433156</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>480574</t>
+          <t>479535</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>64,52%</t>
+          <t>64,62%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>71,7%</t>
+          <t>71,54%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>290889</t>
+          <t>291060</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>350213</t>
+          <t>351219</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>25,31%</t>
+          <t>25,33%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>30,47%</t>
+          <t>30,56%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>251338</t>
+          <t>252919</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>303803</t>
+          <t>302925</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>37,76%</t>
+          <t>37,99%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>45,64%</t>
+          <t>45,51%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>559105</t>
+          <t>558526</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>641664</t>
+          <t>637793</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>30,81%</t>
+          <t>30,77%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>35,35%</t>
+          <t>35,14%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>799071</t>
+          <t>798065</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>858395</t>
+          <t>858224</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>69,53%</t>
+          <t>69,44%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>74,69%</t>
+          <t>74,67%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>361882</t>
+          <t>362760</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>414347</t>
+          <t>412766</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>54,36%</t>
+          <t>54,49%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>62,24%</t>
+          <t>62,01%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1173305</t>
+          <t>1177176</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1255864</t>
+          <t>1256443</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>64,65%</t>
+          <t>64,86%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>69,19%</t>
+          <t>69,23%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>86095</t>
+          <t>87336</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>118557</t>
+          <t>120641</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>27,16%</t>
+          <t>27,55%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>37,4%</t>
+          <t>38,05%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>209475</t>
+          <t>204731</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>254419</t>
+          <t>252401</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>40,48%</t>
+          <t>39,57%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>49,17%</t>
+          <t>48,78%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>304179</t>
+          <t>302977</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>360972</t>
+          <t>359372</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>36,45%</t>
+          <t>36,31%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>43,26%</t>
+          <t>43,07%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>198478</t>
+          <t>196394</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>230940</t>
+          <t>229699</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>62,6%</t>
+          <t>61,95%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>72,84%</t>
+          <t>72,45%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>263002</t>
+          <t>265020</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>307946</t>
+          <t>312690</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>50,83%</t>
+          <t>51,22%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>59,52%</t>
+          <t>60,43%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>473484</t>
+          <t>475084</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>530277</t>
+          <t>531479</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>56,74%</t>
+          <t>56,93%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>63,55%</t>
+          <t>63,69%</t>
         </is>
       </c>
     </row>
@@ -2448,12 +2448,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>115892</t>
+          <t>114289</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>149047</t>
+          <t>147847</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2463,12 +2463,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>39,71%</t>
+          <t>39,16%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>51,07%</t>
+          <t>50,66%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>336711</t>
+          <t>338656</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>398276</t>
+          <t>395735</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2498,12 +2498,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>29,93%</t>
+          <t>30,11%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>35,41%</t>
+          <t>35,18%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>463964</t>
+          <t>466027</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>535907</t>
+          <t>539178</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2533,12 +2533,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>32,75%</t>
+          <t>32,89%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>37,83%</t>
+          <t>38,06%</t>
         </is>
       </c>
     </row>
@@ -2561,12 +2561,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>142818</t>
+          <t>144018</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>175973</t>
+          <t>177576</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2576,12 +2576,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>48,93%</t>
+          <t>49,34%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>60,29%</t>
+          <t>60,84%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>726627</t>
+          <t>729168</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>788192</t>
+          <t>786247</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2611,12 +2611,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>64,59%</t>
+          <t>64,82%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>70,07%</t>
+          <t>69,89%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>880861</t>
+          <t>877590</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>952804</t>
+          <t>950741</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2646,12 +2646,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>62,17%</t>
+          <t>61,94%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>67,25%</t>
+          <t>67,11%</t>
         </is>
       </c>
     </row>
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>817906</t>
+          <t>821569</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>921824</t>
+          <t>918171</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2806,12 +2806,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>26,86%</t>
+          <t>26,98%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>30,27%</t>
+          <t>30,15%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>1089181</t>
+          <t>1093542</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>1197981</t>
+          <t>1198857</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2841,12 +2841,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>35,23%</t>
+          <t>35,37%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>38,75%</t>
+          <t>38,78%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1941066</t>
+          <t>1948832</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>2094859</t>
+          <t>2095516</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>31,63%</t>
+          <t>31,76%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>34,14%</t>
+          <t>34,15%</t>
         </is>
       </c>
     </row>
@@ -2904,12 +2904,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>2123689</t>
+          <t>2127342</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>2227607</t>
+          <t>2223944</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>69,73%</t>
+          <t>69,85%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>73,14%</t>
+          <t>73,02%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>1893333</t>
+          <t>1892457</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>2002133</t>
+          <t>1997772</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,12 +2954,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>61,25%</t>
+          <t>61,22%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>64,77%</t>
+          <t>64,63%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>4041967</t>
+          <t>4041310</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>4195760</t>
+          <t>4187994</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2989,12 +2989,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>65,86%</t>
+          <t>65,85%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>68,37%</t>
+          <t>68,24%</t>
         </is>
       </c>
     </row>
@@ -3173,7 +3173,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si tienen algún familiar que fuma habitualmente en casa en 2012</t>
+          <t>Población según si tienen algún familiar que fuma habitualmente en casa en 2012 (tasa de respuesta: 99,45%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3368,12 +3368,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>97816</t>
+          <t>96449</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>136082</t>
+          <t>137144</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3383,12 +3383,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>24,26%</t>
+          <t>23,93%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>33,76%</t>
+          <t>34,02%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3403,12 +3403,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>76284</t>
+          <t>76942</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>112215</t>
+          <t>112106</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3418,12 +3418,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>25,99%</t>
+          <t>26,22%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>38,24%</t>
+          <t>38,2%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3438,12 +3438,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>182995</t>
+          <t>184089</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>235902</t>
+          <t>234527</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3453,12 +3453,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>26,27%</t>
+          <t>26,43%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>33,87%</t>
+          <t>33,67%</t>
         </is>
       </c>
     </row>
@@ -3481,12 +3481,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>267041</t>
+          <t>265979</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>305307</t>
+          <t>306674</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3496,12 +3496,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>66,24%</t>
+          <t>65,98%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>75,74%</t>
+          <t>76,07%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3516,12 +3516,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>181254</t>
+          <t>181363</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>217185</t>
+          <t>216527</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3531,12 +3531,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>61,76%</t>
+          <t>61,8%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>74,01%</t>
+          <t>73,78%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3551,12 +3551,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>460690</t>
+          <t>462065</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>513597</t>
+          <t>512503</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3566,12 +3566,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>66,13%</t>
+          <t>66,33%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>73,73%</t>
+          <t>73,57%</t>
         </is>
       </c>
     </row>
@@ -3711,12 +3711,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>88009</t>
+          <t>87037</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>127616</t>
+          <t>126439</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3726,12 +3726,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>21,85%</t>
+          <t>21,61%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>31,69%</t>
+          <t>31,4%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3746,12 +3746,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>86205</t>
+          <t>87743</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>121314</t>
+          <t>122145</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3761,12 +3761,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>26,68%</t>
+          <t>27,15%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>37,54%</t>
+          <t>37,8%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3781,12 +3781,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>187878</t>
+          <t>185074</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>238346</t>
+          <t>238326</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3796,12 +3796,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>25,88%</t>
+          <t>25,5%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>32,84%</t>
+          <t>32,83%</t>
         </is>
       </c>
     </row>
@@ -3824,12 +3824,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>275117</t>
+          <t>276294</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>314724</t>
+          <t>315696</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3839,12 +3839,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>68,31%</t>
+          <t>68,6%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>78,15%</t>
+          <t>78,39%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3859,12 +3859,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>201819</t>
+          <t>200988</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>236928</t>
+          <t>235390</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3874,12 +3874,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>62,46%</t>
+          <t>62,2%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>73,32%</t>
+          <t>72,85%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3894,12 +3894,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>487521</t>
+          <t>487541</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>537989</t>
+          <t>540793</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3909,12 +3909,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>67,16%</t>
+          <t>67,17%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>74,12%</t>
+          <t>74,5%</t>
         </is>
       </c>
     </row>
@@ -4054,12 +4054,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>182712</t>
+          <t>182659</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>230592</t>
+          <t>228832</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4074,7 +4074,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>37,94%</t>
+          <t>37,65%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4089,12 +4089,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>89635</t>
+          <t>89731</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>119916</t>
+          <t>120728</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4104,12 +4104,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>37,28%</t>
+          <t>37,32%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>49,87%</t>
+          <t>50,21%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4124,12 +4124,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>281901</t>
+          <t>283917</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>340441</t>
+          <t>340303</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4139,12 +4139,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>33,24%</t>
+          <t>33,47%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>40,14%</t>
+          <t>40,12%</t>
         </is>
       </c>
     </row>
@@ -4167,12 +4167,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>377145</t>
+          <t>378905</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>425025</t>
+          <t>425078</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4182,7 +4182,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>62,06%</t>
+          <t>62,35%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -4202,12 +4202,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>120532</t>
+          <t>119720</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>150813</t>
+          <t>150717</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4217,12 +4217,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>50,13%</t>
+          <t>49,79%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>62,72%</t>
+          <t>62,68%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4237,12 +4237,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>507744</t>
+          <t>507882</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>566284</t>
+          <t>564268</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4252,12 +4252,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>59,86%</t>
+          <t>59,88%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>66,76%</t>
+          <t>66,53%</t>
         </is>
       </c>
     </row>
@@ -4397,12 +4397,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>336007</t>
+          <t>335317</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>401971</t>
+          <t>400254</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4412,12 +4412,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>30,4%</t>
+          <t>30,33%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>36,36%</t>
+          <t>36,21%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4432,12 +4432,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>285318</t>
+          <t>286004</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>340573</t>
+          <t>339583</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4447,12 +4447,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>38,28%</t>
+          <t>38,38%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>45,7%</t>
+          <t>45,56%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4467,12 +4467,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>639604</t>
+          <t>634926</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>727338</t>
+          <t>722785</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4482,12 +4482,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>34,56%</t>
+          <t>34,31%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>39,3%</t>
+          <t>39,06%</t>
         </is>
       </c>
     </row>
@@ -4510,12 +4510,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>703420</t>
+          <t>705137</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>769384</t>
+          <t>770074</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4525,12 +4525,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>63,64%</t>
+          <t>63,79%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>69,6%</t>
+          <t>69,67%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4545,12 +4545,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>404701</t>
+          <t>405691</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>459956</t>
+          <t>459270</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>54,3%</t>
+          <t>54,44%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>61,72%</t>
+          <t>61,62%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4580,12 +4580,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1123327</t>
+          <t>1127880</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1211061</t>
+          <t>1215739</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4595,12 +4595,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>60,7%</t>
+          <t>60,94%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>65,44%</t>
+          <t>65,69%</t>
         </is>
       </c>
     </row>
@@ -4740,12 +4740,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>140920</t>
+          <t>141882</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>185565</t>
+          <t>184975</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4755,12 +4755,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>28,61%</t>
+          <t>28,8%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>37,67%</t>
+          <t>37,55%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4775,12 +4775,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>269261</t>
+          <t>271588</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>326164</t>
+          <t>325471</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4790,12 +4790,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>37,12%</t>
+          <t>37,44%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>44,96%</t>
+          <t>44,87%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>426544</t>
+          <t>425920</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>494784</t>
+          <t>494809</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4825,12 +4825,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>35,02%</t>
+          <t>34,97%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>40,62%</t>
+          <t>40,63%</t>
         </is>
       </c>
     </row>
@@ -4853,12 +4853,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>306998</t>
+          <t>307588</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>351643</t>
+          <t>350681</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4868,12 +4868,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>62,33%</t>
+          <t>62,45%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>71,39%</t>
+          <t>71,2%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4888,12 +4888,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>399233</t>
+          <t>399926</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>456136</t>
+          <t>453809</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4903,12 +4903,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>55,04%</t>
+          <t>55,13%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>62,88%</t>
+          <t>62,56%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4923,12 +4923,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>723175</t>
+          <t>723150</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>791415</t>
+          <t>792039</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4938,12 +4938,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>59,38%</t>
+          <t>59,37%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>64,98%</t>
+          <t>65,03%</t>
         </is>
       </c>
     </row>
@@ -5083,12 +5083,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>97324</t>
+          <t>96917</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>127997</t>
+          <t>128142</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5098,12 +5098,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>36,86%</t>
+          <t>36,7%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>48,47%</t>
+          <t>48,53%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5118,12 +5118,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>357893</t>
+          <t>358209</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>422279</t>
+          <t>422047</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5133,12 +5133,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>34,85%</t>
+          <t>34,88%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>41,12%</t>
+          <t>41,1%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>466336</t>
+          <t>464156</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>539402</t>
+          <t>534509</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5168,12 +5168,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>36,12%</t>
+          <t>35,95%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>41,78%</t>
+          <t>41,4%</t>
         </is>
       </c>
     </row>
@@ -5196,12 +5196,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>136064</t>
+          <t>135919</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>166737</t>
+          <t>167144</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5211,12 +5211,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>51,53%</t>
+          <t>51,47%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>63,14%</t>
+          <t>63,3%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5231,12 +5231,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>604609</t>
+          <t>604841</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>668995</t>
+          <t>668679</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5246,12 +5246,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>58,88%</t>
+          <t>58,9%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>65,15%</t>
+          <t>65,12%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5266,12 +5266,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>751547</t>
+          <t>756440</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>824613</t>
+          <t>826793</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5281,12 +5281,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>58,22%</t>
+          <t>58,6%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>63,88%</t>
+          <t>64,05%</t>
         </is>
       </c>
     </row>
@@ -5426,12 +5426,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>1020993</t>
+          <t>1021170</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>1129024</t>
+          <t>1133224</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5446,7 +5446,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>34,47%</t>
+          <t>34,6%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5461,12 +5461,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>1240534</t>
+          <t>1239312</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>1356262</t>
+          <t>1354725</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5476,12 +5476,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>36,98%</t>
+          <t>36,94%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>40,43%</t>
+          <t>40,38%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>2298569</t>
+          <t>2289821</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>2457377</t>
+          <t>2457704</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>34,67%</t>
+          <t>34,54%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>37,06%</t>
+          <t>37,07%</t>
         </is>
       </c>
     </row>
@@ -5539,12 +5539,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>2146584</t>
+          <t>2142384</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>2254615</t>
+          <t>2254438</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5554,7 +5554,7 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>65,53%</t>
+          <t>65,4%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
@@ -5574,12 +5574,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>1998346</t>
+          <t>1999883</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>2114074</t>
+          <t>2115296</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5589,12 +5589,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>59,57%</t>
+          <t>59,62%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>63,02%</t>
+          <t>63,06%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5609,12 +5609,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>4172840</t>
+          <t>4172513</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>4331648</t>
+          <t>4340396</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5624,12 +5624,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>62,94%</t>
+          <t>62,93%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>65,33%</t>
+          <t>65,46%</t>
         </is>
       </c>
     </row>
@@ -5808,7 +5808,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si tienen algún familiar que fuma habitualmente en casa en 2016</t>
+          <t>Población según si tienen algún familiar que fuma habitualmente en casa en 2016 (tasa de respuesta: 99,58%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -6003,12 +6003,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>57457</t>
+          <t>56781</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>89908</t>
+          <t>88310</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6018,12 +6018,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>15,09%</t>
+          <t>14,91%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>23,61%</t>
+          <t>23,19%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6038,12 +6038,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>58688</t>
+          <t>60059</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>90113</t>
+          <t>89100</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6053,12 +6053,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>18,49%</t>
+          <t>18,92%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>28,39%</t>
+          <t>28,07%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6073,12 +6073,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>124163</t>
+          <t>123604</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>167434</t>
+          <t>168563</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6088,12 +6088,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>17,78%</t>
+          <t>17,7%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>23,98%</t>
+          <t>24,14%</t>
         </is>
       </c>
     </row>
@@ -6116,12 +6116,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>290855</t>
+          <t>292453</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>323306</t>
+          <t>323982</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6131,12 +6131,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>76,39%</t>
+          <t>76,81%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>84,91%</t>
+          <t>85,09%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6151,12 +6151,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>227335</t>
+          <t>228348</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>258760</t>
+          <t>257389</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6166,12 +6166,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>71,61%</t>
+          <t>71,93%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>81,51%</t>
+          <t>81,08%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6186,12 +6186,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>530776</t>
+          <t>529647</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>574047</t>
+          <t>574606</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6201,12 +6201,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>76,02%</t>
+          <t>75,86%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>82,22%</t>
+          <t>82,3%</t>
         </is>
       </c>
     </row>
@@ -6346,12 +6346,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>56485</t>
+          <t>56292</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>85654</t>
+          <t>86825</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -6361,12 +6361,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>15,9%</t>
+          <t>15,84%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>24,11%</t>
+          <t>24,44%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6381,12 +6381,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>62604</t>
+          <t>64205</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>94536</t>
+          <t>97713</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6396,12 +6396,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>18,3%</t>
+          <t>18,77%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>27,64%</t>
+          <t>28,56%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6416,12 +6416,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>128176</t>
+          <t>130252</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>172679</t>
+          <t>172925</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -6431,12 +6431,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>18,38%</t>
+          <t>18,68%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>24,76%</t>
+          <t>24,8%</t>
         </is>
       </c>
     </row>
@@ -6459,12 +6459,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>269631</t>
+          <t>268460</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>298800</t>
+          <t>298993</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -6474,12 +6474,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>75,89%</t>
+          <t>75,56%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>84,1%</t>
+          <t>84,16%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6494,12 +6494,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>247537</t>
+          <t>244360</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>279469</t>
+          <t>277868</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -6509,12 +6509,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>72,36%</t>
+          <t>71,44%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>81,7%</t>
+          <t>81,23%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6529,12 +6529,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>524679</t>
+          <t>524433</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>569182</t>
+          <t>567106</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -6544,12 +6544,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>75,24%</t>
+          <t>75,2%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>81,62%</t>
+          <t>81,32%</t>
         </is>
       </c>
     </row>
@@ -6689,12 +6689,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>105826</t>
+          <t>106687</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>147199</t>
+          <t>146391</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6704,12 +6704,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>21,7%</t>
+          <t>21,87%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>30,18%</t>
+          <t>30,01%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6724,12 +6724,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>23597</t>
+          <t>23872</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>46015</t>
+          <t>44788</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6739,12 +6739,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>15,41%</t>
+          <t>15,59%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>30,04%</t>
+          <t>29,24%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6759,12 +6759,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>136376</t>
+          <t>135074</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>182335</t>
+          <t>181607</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6774,12 +6774,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>21,28%</t>
+          <t>21,07%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>28,45%</t>
+          <t>28,34%</t>
         </is>
       </c>
     </row>
@@ -6802,12 +6802,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>340567</t>
+          <t>341375</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>381940</t>
+          <t>381079</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -6817,12 +6817,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>69,82%</t>
+          <t>69,99%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>78,3%</t>
+          <t>78,13%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6837,12 +6837,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>107146</t>
+          <t>108373</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>129564</t>
+          <t>129289</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -6852,12 +6852,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>69,96%</t>
+          <t>70,76%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>84,59%</t>
+          <t>84,41%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6872,12 +6872,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>458592</t>
+          <t>459320</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>504551</t>
+          <t>505853</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6887,12 +6887,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>71,55%</t>
+          <t>71,66%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>78,72%</t>
+          <t>78,93%</t>
         </is>
       </c>
     </row>
@@ -7032,12 +7032,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>264476</t>
+          <t>263681</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>320135</t>
+          <t>321480</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7047,12 +7047,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>24,53%</t>
+          <t>24,45%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>29,69%</t>
+          <t>29,82%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>205089</t>
+          <t>206654</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>254462</t>
+          <t>258990</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7082,12 +7082,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>26,62%</t>
+          <t>26,82%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>33,03%</t>
+          <t>33,62%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7102,12 +7102,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>483370</t>
+          <t>481807</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>561841</t>
+          <t>560144</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7117,12 +7117,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>26,15%</t>
+          <t>26,06%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>30,39%</t>
+          <t>30,3%</t>
         </is>
       </c>
     </row>
@@ -7145,12 +7145,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>758102</t>
+          <t>756757</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>813761</t>
+          <t>814556</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7160,12 +7160,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>70,31%</t>
+          <t>70,18%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>75,47%</t>
+          <t>75,55%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7180,12 +7180,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>515984</t>
+          <t>511456</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>565357</t>
+          <t>563792</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7195,12 +7195,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>66,97%</t>
+          <t>66,38%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>73,38%</t>
+          <t>73,18%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7215,12 +7215,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1286842</t>
+          <t>1288539</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1365313</t>
+          <t>1366876</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7230,12 +7230,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>69,61%</t>
+          <t>69,7%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>73,85%</t>
+          <t>73,94%</t>
         </is>
       </c>
     </row>
@@ -7375,12 +7375,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>115341</t>
+          <t>116986</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>155932</t>
+          <t>156103</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7390,12 +7390,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>20,62%</t>
+          <t>20,91%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>27,88%</t>
+          <t>27,91%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7410,12 +7410,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>185720</t>
+          <t>186533</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>232855</t>
+          <t>232979</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7425,12 +7425,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>27,03%</t>
+          <t>27,15%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>33,89%</t>
+          <t>33,91%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -7445,12 +7445,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>312516</t>
+          <t>312863</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>375127</t>
+          <t>375112</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -7460,7 +7460,7 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>25,07%</t>
+          <t>25,1%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
@@ -7488,12 +7488,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>403432</t>
+          <t>403261</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>444023</t>
+          <t>442378</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -7503,12 +7503,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>72,12%</t>
+          <t>72,09%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>79,38%</t>
+          <t>79,09%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -7523,12 +7523,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>454152</t>
+          <t>454028</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>501287</t>
+          <t>500474</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -7538,12 +7538,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>66,11%</t>
+          <t>66,09%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>72,97%</t>
+          <t>72,85%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -7558,12 +7558,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>871244</t>
+          <t>871259</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>933855</t>
+          <t>933508</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -7578,7 +7578,7 @@
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>74,93%</t>
+          <t>74,9%</t>
         </is>
       </c>
     </row>
@@ -7718,12 +7718,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>82962</t>
+          <t>81810</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>115167</t>
+          <t>113818</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -7733,12 +7733,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>29,53%</t>
+          <t>29,12%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>41,0%</t>
+          <t>40,52%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -7753,12 +7753,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>222470</t>
+          <t>217467</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>276962</t>
+          <t>275182</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -7768,12 +7768,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>22,24%</t>
+          <t>21,74%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>27,69%</t>
+          <t>27,51%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -7788,12 +7788,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>312851</t>
+          <t>311666</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>378446</t>
+          <t>378977</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -7803,12 +7803,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>24,42%</t>
+          <t>24,33%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>29,54%</t>
+          <t>29,58%</t>
         </is>
       </c>
     </row>
@@ -7831,12 +7831,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>165732</t>
+          <t>167081</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>197937</t>
+          <t>199089</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -7846,12 +7846,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>59,0%</t>
+          <t>59,48%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>70,47%</t>
+          <t>70,88%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -7866,12 +7866,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>723294</t>
+          <t>725074</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>777786</t>
+          <t>782789</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -7881,12 +7881,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>72,31%</t>
+          <t>72,49%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>77,76%</t>
+          <t>78,26%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -7901,12 +7901,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>902709</t>
+          <t>902178</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>968304</t>
+          <t>969489</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -7916,12 +7916,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>70,46%</t>
+          <t>70,42%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>75,58%</t>
+          <t>75,67%</t>
         </is>
       </c>
     </row>
@@ -8061,12 +8061,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>739412</t>
+          <t>743845</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>843983</t>
+          <t>839472</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8076,12 +8076,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>23,53%</t>
+          <t>23,67%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>26,86%</t>
+          <t>26,72%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8096,12 +8096,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>818088</t>
+          <t>821065</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>919717</t>
+          <t>925357</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8111,12 +8111,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>25,01%</t>
+          <t>25,11%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>28,12%</t>
+          <t>28,29%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8131,12 +8131,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1589391</t>
+          <t>1587033</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1732406</t>
+          <t>1732832</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8146,7 +8146,7 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>24,79%</t>
+          <t>24,75%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
@@ -8174,12 +8174,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>2298330</t>
+          <t>2302841</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>2402901</t>
+          <t>2398468</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -8189,12 +8189,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>73,14%</t>
+          <t>73,28%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>76,47%</t>
+          <t>76,33%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -8209,12 +8209,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>2350674</t>
+          <t>2345034</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>2452303</t>
+          <t>2449326</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -8224,12 +8224,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>71,88%</t>
+          <t>71,71%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>74,99%</t>
+          <t>74,89%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -8244,12 +8244,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>4680298</t>
+          <t>4679872</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>4823313</t>
+          <t>4825671</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8264,7 +8264,7 @@
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>75,21%</t>
+          <t>75,25%</t>
         </is>
       </c>
     </row>
@@ -8443,7 +8443,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si tienen algún familiar que fuma habitualmente en casa en 2023</t>
+          <t>Población según si tienen algún familiar que fuma habitualmente en casa en 2023 (tasa de respuesta: 99,89%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -8638,12 +8638,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>28990</t>
+          <t>29814</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>56448</t>
+          <t>57670</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -8653,12 +8653,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>6,24%</t>
+          <t>6,41%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>12,14%</t>
+          <t>12,4%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -8673,12 +8673,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>31547</t>
+          <t>32341</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>53461</t>
+          <t>54126</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -8688,12 +8688,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>7,62%</t>
+          <t>7,81%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>12,91%</t>
+          <t>13,07%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -8708,12 +8708,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>67801</t>
+          <t>67714</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>104888</t>
+          <t>102757</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -8723,12 +8723,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>7,71%</t>
+          <t>7,7%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>11,93%</t>
+          <t>11,69%</t>
         </is>
       </c>
     </row>
@@ -8751,12 +8751,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>408500</t>
+          <t>407278</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>435958</t>
+          <t>435134</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -8766,12 +8766,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>87,86%</t>
+          <t>87,6%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>93,76%</t>
+          <t>93,59%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -8786,12 +8786,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>360641</t>
+          <t>359976</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>382555</t>
+          <t>381761</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -8801,12 +8801,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>87,09%</t>
+          <t>86,93%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>92,38%</t>
+          <t>92,19%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -8821,12 +8821,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>774163</t>
+          <t>776294</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>811250</t>
+          <t>811337</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -8836,12 +8836,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>88,07%</t>
+          <t>88,31%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>92,29%</t>
+          <t>92,3%</t>
         </is>
       </c>
     </row>
@@ -8981,12 +8981,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>25610</t>
+          <t>25978</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>54168</t>
+          <t>58870</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -8996,12 +8996,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>6,14%</t>
+          <t>6,23%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>12,98%</t>
+          <t>14,11%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -9016,12 +9016,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>34955</t>
+          <t>34807</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>57744</t>
+          <t>59064</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -9031,12 +9031,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>9,73%</t>
+          <t>9,69%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>16,07%</t>
+          <t>16,44%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -9051,12 +9051,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>67247</t>
+          <t>66085</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>107966</t>
+          <t>104048</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -9066,12 +9066,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>8,66%</t>
+          <t>8,51%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>13,91%</t>
+          <t>13,4%</t>
         </is>
       </c>
     </row>
@@ -9094,12 +9094,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>363000</t>
+          <t>358298</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>391558</t>
+          <t>391190</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -9109,12 +9109,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>87,02%</t>
+          <t>85,89%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>93,86%</t>
+          <t>93,77%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -9129,12 +9129,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>301484</t>
+          <t>300164</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>324273</t>
+          <t>324421</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -9144,12 +9144,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>83,93%</t>
+          <t>83,56%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>90,27%</t>
+          <t>90,31%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -9164,12 +9164,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>668431</t>
+          <t>672349</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>709150</t>
+          <t>710312</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -9179,12 +9179,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>86,09%</t>
+          <t>86,6%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>91,34%</t>
+          <t>91,49%</t>
         </is>
       </c>
     </row>
@@ -9324,12 +9324,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>47703</t>
+          <t>47633</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>506699</t>
+          <t>493456</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -9339,12 +9339,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>7,57%</t>
+          <t>7,56%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>80,46%</t>
+          <t>78,35%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -9359,12 +9359,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>8105</t>
+          <t>7973</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>19196</t>
+          <t>19158</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -9374,12 +9374,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>5,45%</t>
+          <t>5,36%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>12,9%</t>
+          <t>12,87%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -9394,12 +9394,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>60719</t>
+          <t>60505</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>560796</t>
+          <t>579342</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -9409,12 +9409,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>7,8%</t>
+          <t>7,77%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>72,03%</t>
+          <t>74,41%</t>
         </is>
       </c>
     </row>
@@ -9437,12 +9437,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>123072</t>
+          <t>136315</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>582068</t>
+          <t>582138</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -9452,12 +9452,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>19,54%</t>
+          <t>21,65%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>92,43%</t>
+          <t>92,44%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -9472,12 +9472,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>129635</t>
+          <t>129673</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>140726</t>
+          <t>140858</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -9487,12 +9487,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>87,1%</t>
+          <t>87,13%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>94,55%</t>
+          <t>94,64%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -9507,12 +9507,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>217807</t>
+          <t>199261</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>717884</t>
+          <t>718098</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -9522,12 +9522,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>27,97%</t>
+          <t>25,59%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>92,2%</t>
+          <t>92,23%</t>
         </is>
       </c>
     </row>
@@ -9667,12 +9667,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>100704</t>
+          <t>101631</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>153330</t>
+          <t>151686</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -9682,12 +9682,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>10,85%</t>
+          <t>10,95%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>16,53%</t>
+          <t>16,35%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -9702,12 +9702,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>69243</t>
+          <t>59946</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>178272</t>
+          <t>176237</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -9717,12 +9717,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>7,5%</t>
+          <t>6,49%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>19,3%</t>
+          <t>19,08%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -9737,12 +9737,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>173885</t>
+          <t>168884</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>302677</t>
+          <t>302248</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -9752,12 +9752,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>9,39%</t>
+          <t>9,12%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>16,35%</t>
+          <t>16,33%</t>
         </is>
       </c>
     </row>
@@ -9780,12 +9780,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>774436</t>
+          <t>776080</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>827062</t>
+          <t>826135</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -9795,12 +9795,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>83,47%</t>
+          <t>83,65%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>89,15%</t>
+          <t>89,05%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -9815,12 +9815,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>745352</t>
+          <t>747387</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>854381</t>
+          <t>863678</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -9830,12 +9830,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>80,7%</t>
+          <t>80,92%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>92,5%</t>
+          <t>93,51%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -9850,12 +9850,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1548713</t>
+          <t>1549142</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1677505</t>
+          <t>1682506</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -9865,12 +9865,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>83,65%</t>
+          <t>83,67%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>90,61%</t>
+          <t>90,88%</t>
         </is>
       </c>
     </row>
@@ -10010,12 +10010,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>44516</t>
+          <t>44162</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>74743</t>
+          <t>74531</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -10025,12 +10025,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>10,55%</t>
+          <t>10,47%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>17,72%</t>
+          <t>17,67%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -10045,12 +10045,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>76733</t>
+          <t>76746</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>127419</t>
+          <t>126755</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -10065,7 +10065,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>16,51%</t>
+          <t>16,43%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -10080,12 +10080,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>132287</t>
+          <t>133535</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>194576</t>
+          <t>191929</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -10095,12 +10095,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>11,08%</t>
+          <t>11,19%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>16,3%</t>
+          <t>16,08%</t>
         </is>
       </c>
     </row>
@@ -10123,12 +10123,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>347094</t>
+          <t>347306</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>377321</t>
+          <t>377675</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -10138,12 +10138,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>82,28%</t>
+          <t>82,33%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>89,45%</t>
+          <t>89,53%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -10158,12 +10158,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>644291</t>
+          <t>644955</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>694977</t>
+          <t>694964</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -10173,7 +10173,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>83,49%</t>
+          <t>83,57%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -10193,12 +10193,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>998971</t>
+          <t>1001618</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1061260</t>
+          <t>1060012</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -10208,12 +10208,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>83,7%</t>
+          <t>83,92%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>88,92%</t>
+          <t>88,81%</t>
         </is>
       </c>
     </row>
@@ -10353,12 +10353,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>18479</t>
+          <t>19582</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>56905</t>
+          <t>57138</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -10368,12 +10368,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>8,11%</t>
+          <t>8,59%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>24,97%</t>
+          <t>25,08%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -10388,12 +10388,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>64714</t>
+          <t>65627</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>107222</t>
+          <t>107036</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -10403,12 +10403,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>9,68%</t>
+          <t>9,81%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>16,03%</t>
+          <t>16,0%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -10423,12 +10423,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>94986</t>
+          <t>92752</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>146469</t>
+          <t>144375</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -10438,12 +10438,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>10,59%</t>
+          <t>10,34%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>16,33%</t>
+          <t>16,1%</t>
         </is>
       </c>
     </row>
@@ -10466,12 +10466,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>170954</t>
+          <t>170721</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>209380</t>
+          <t>208277</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -10481,12 +10481,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>75,03%</t>
+          <t>74,92%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>91,89%</t>
+          <t>91,41%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -10501,12 +10501,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>561603</t>
+          <t>561789</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>604111</t>
+          <t>603198</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -10516,12 +10516,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>83,97%</t>
+          <t>84,0%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>90,32%</t>
+          <t>90,19%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -10536,12 +10536,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>750215</t>
+          <t>752309</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>801698</t>
+          <t>803932</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -10551,12 +10551,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>83,67%</t>
+          <t>83,9%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>89,41%</t>
+          <t>89,66%</t>
         </is>
       </c>
     </row>
@@ -10696,12 +10696,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>345463</t>
+          <t>344351</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>1289217</t>
+          <t>1232840</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -10711,12 +10711,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>11,18%</t>
+          <t>11,15%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>41,73%</t>
+          <t>39,91%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -10731,12 +10731,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>329842</t>
+          <t>343902</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>469362</t>
+          <t>470313</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -10746,12 +10746,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>10,04%</t>
+          <t>10,46%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>14,28%</t>
+          <t>14,31%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -10766,12 +10766,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>755238</t>
+          <t>749560</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1614244</t>
+          <t>1773213</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -10781,12 +10781,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>11,85%</t>
+          <t>11,76%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>25,32%</t>
+          <t>27,81%</t>
         </is>
       </c>
     </row>
@@ -10809,12 +10809,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>1800134</t>
+          <t>1856511</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>2743888</t>
+          <t>2745000</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -10824,12 +10824,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>58,27%</t>
+          <t>60,09%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>88,82%</t>
+          <t>88,85%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -10844,12 +10844,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>2816959</t>
+          <t>2816008</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>2956479</t>
+          <t>2942419</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -10859,12 +10859,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>85,72%</t>
+          <t>85,69%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>89,96%</t>
+          <t>89,54%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -10874,17 +10874,17 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>5381196</t>
+          <t>5381197</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>4761427</t>
+          <t>4602459</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>5620433</t>
+          <t>5626112</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -10894,12 +10894,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>74,68%</t>
+          <t>72,19%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>88,15%</t>
+          <t>88,24%</t>
         </is>
       </c>
     </row>
@@ -10987,17 +10987,17 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>6375671</t>
+          <t>6375672</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>6375671</t>
+          <t>6375672</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>6375671</t>
+          <t>6375672</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">

--- a/data/trans_orig/P26-Clase-trans_orig.xlsx
+++ b/data/trans_orig/P26-Clase-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>79437</t>
+          <t>81147</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>115381</t>
+          <t>117462</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>17,98%</t>
+          <t>18,36%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>26,11%</t>
+          <t>26,58%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>62006</t>
+          <t>62623</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>91966</t>
+          <t>91524</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>22,38%</t>
+          <t>22,6%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>33,19%</t>
+          <t>33,03%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>149346</t>
+          <t>150689</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>195537</t>
+          <t>196778</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>20,77%</t>
+          <t>20,96%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>27,2%</t>
+          <t>27,37%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>326539</t>
+          <t>324458</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>362483</t>
+          <t>360773</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>73,89%</t>
+          <t>73,42%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>82,02%</t>
+          <t>81,64%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>185113</t>
+          <t>185555</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>215073</t>
+          <t>214456</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>66,81%</t>
+          <t>66,97%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>77,62%</t>
+          <t>77,4%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>523462</t>
+          <t>522221</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>569653</t>
+          <t>568310</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>72,8%</t>
+          <t>72,63%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>79,23%</t>
+          <t>79,04%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>60957</t>
+          <t>59254</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>92329</t>
+          <t>93656</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>18,43%</t>
+          <t>17,91%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>27,91%</t>
+          <t>28,31%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>109900</t>
+          <t>109067</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>145973</t>
+          <t>144328</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>31,35%</t>
+          <t>31,11%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>41,64%</t>
+          <t>41,17%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>177721</t>
+          <t>178226</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>227059</t>
+          <t>227458</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>26,08%</t>
+          <t>26,16%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>33,32%</t>
+          <t>33,38%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>238441</t>
+          <t>237114</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>269813</t>
+          <t>271516</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>72,09%</t>
+          <t>71,69%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>81,57%</t>
+          <t>82,09%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>204614</t>
+          <t>206259</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>240687</t>
+          <t>241520</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>58,36%</t>
+          <t>58,83%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>68,65%</t>
+          <t>68,89%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>454299</t>
+          <t>453900</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>503637</t>
+          <t>503132</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>66,68%</t>
+          <t>66,62%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>73,92%</t>
+          <t>73,84%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>126330</t>
+          <t>124681</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>165797</t>
+          <t>165387</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>24,55%</t>
+          <t>24,23%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>32,22%</t>
+          <t>32,14%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>56155</t>
+          <t>56040</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>80205</t>
+          <t>80878</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>36,08%</t>
+          <t>36,01%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>51,53%</t>
+          <t>51,97%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>190741</t>
+          <t>189576</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>237120</t>
+          <t>236412</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>28,46%</t>
+          <t>28,28%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>35,38%</t>
+          <t>35,27%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>348841</t>
+          <t>349251</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>388308</t>
+          <t>389957</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>67,78%</t>
+          <t>67,86%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>75,45%</t>
+          <t>75,77%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>75434</t>
+          <t>74761</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>99484</t>
+          <t>99599</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>48,47%</t>
+          <t>48,03%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>63,92%</t>
+          <t>63,99%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>433156</t>
+          <t>433864</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>479535</t>
+          <t>480700</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>64,62%</t>
+          <t>64,73%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>71,54%</t>
+          <t>71,72%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>291060</t>
+          <t>289413</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>351219</t>
+          <t>349975</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,82 +1777,82 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>25,33%</t>
+          <t>25,18%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
+          <t>30,45%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>270</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>277927</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>253319</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>305293</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>41,75%</t>
+        </is>
+      </c>
+      <c r="O13" s="2" t="inlineStr">
+        <is>
+          <t>38,05%</t>
+        </is>
+      </c>
+      <c r="P13" s="2" t="inlineStr">
+        <is>
+          <t>45,86%</t>
+        </is>
+      </c>
+      <c r="Q13" s="2" t="inlineStr">
+        <is>
+          <t>582</t>
+        </is>
+      </c>
+      <c r="R13" s="2" t="inlineStr">
+        <is>
+          <t>598432</t>
+        </is>
+      </c>
+      <c r="S13" s="2" t="inlineStr">
+        <is>
+          <t>554713</t>
+        </is>
+      </c>
+      <c r="T13" s="2" t="inlineStr">
+        <is>
+          <t>634102</t>
+        </is>
+      </c>
+      <c r="U13" s="2" t="inlineStr">
+        <is>
+          <t>32,97%</t>
+        </is>
+      </c>
+      <c r="V13" s="2" t="inlineStr">
+        <is>
           <t>30,56%</t>
         </is>
       </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>270</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>277927</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>252919</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>302925</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>41,75%</t>
-        </is>
-      </c>
-      <c r="O13" s="2" t="inlineStr">
-        <is>
-          <t>37,99%</t>
-        </is>
-      </c>
-      <c r="P13" s="2" t="inlineStr">
-        <is>
-          <t>45,51%</t>
-        </is>
-      </c>
-      <c r="Q13" s="2" t="inlineStr">
-        <is>
-          <t>582</t>
-        </is>
-      </c>
-      <c r="R13" s="2" t="inlineStr">
-        <is>
-          <t>598432</t>
-        </is>
-      </c>
-      <c r="S13" s="2" t="inlineStr">
-        <is>
-          <t>558526</t>
-        </is>
-      </c>
-      <c r="T13" s="2" t="inlineStr">
-        <is>
-          <t>637793</t>
-        </is>
-      </c>
-      <c r="U13" s="2" t="inlineStr">
-        <is>
-          <t>32,97%</t>
-        </is>
-      </c>
-      <c r="V13" s="2" t="inlineStr">
-        <is>
-          <t>30,77%</t>
-        </is>
-      </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>35,14%</t>
+          <t>34,94%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>798065</t>
+          <t>799309</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>858224</t>
+          <t>859871</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,82 +1890,82 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
+          <t>69,55%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>74,82%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>376</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>387758</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>360392</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>412366</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>58,25%</t>
+        </is>
+      </c>
+      <c r="O14" s="2" t="inlineStr">
+        <is>
+          <t>54,14%</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr">
+        <is>
+          <t>61,95%</t>
+        </is>
+      </c>
+      <c r="Q14" s="2" t="inlineStr">
+        <is>
+          <t>1200</t>
+        </is>
+      </c>
+      <c r="R14" s="2" t="inlineStr">
+        <is>
+          <t>1216537</t>
+        </is>
+      </c>
+      <c r="S14" s="2" t="inlineStr">
+        <is>
+          <t>1180867</t>
+        </is>
+      </c>
+      <c r="T14" s="2" t="inlineStr">
+        <is>
+          <t>1260256</t>
+        </is>
+      </c>
+      <c r="U14" s="2" t="inlineStr">
+        <is>
+          <t>67,03%</t>
+        </is>
+      </c>
+      <c r="V14" s="2" t="inlineStr">
+        <is>
+          <t>65,06%</t>
+        </is>
+      </c>
+      <c r="W14" s="2" t="inlineStr">
+        <is>
           <t>69,44%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>74,67%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>376</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>387758</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>362760</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>412766</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>58,25%</t>
-        </is>
-      </c>
-      <c r="O14" s="2" t="inlineStr">
-        <is>
-          <t>54,49%</t>
-        </is>
-      </c>
-      <c r="P14" s="2" t="inlineStr">
-        <is>
-          <t>62,01%</t>
-        </is>
-      </c>
-      <c r="Q14" s="2" t="inlineStr">
-        <is>
-          <t>1200</t>
-        </is>
-      </c>
-      <c r="R14" s="2" t="inlineStr">
-        <is>
-          <t>1216537</t>
-        </is>
-      </c>
-      <c r="S14" s="2" t="inlineStr">
-        <is>
-          <t>1177176</t>
-        </is>
-      </c>
-      <c r="T14" s="2" t="inlineStr">
-        <is>
-          <t>1256443</t>
-        </is>
-      </c>
-      <c r="U14" s="2" t="inlineStr">
-        <is>
-          <t>67,03%</t>
-        </is>
-      </c>
-      <c r="V14" s="2" t="inlineStr">
-        <is>
-          <t>64,86%</t>
-        </is>
-      </c>
-      <c r="W14" s="2" t="inlineStr">
-        <is>
-          <t>69,23%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>87336</t>
+          <t>87072</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>120641</t>
+          <t>119585</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>27,55%</t>
+          <t>27,46%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>38,05%</t>
+          <t>37,72%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>204731</t>
+          <t>205199</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>252401</t>
+          <t>252185</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>39,57%</t>
+          <t>39,66%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>48,78%</t>
+          <t>48,74%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>302977</t>
+          <t>301475</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>359372</t>
+          <t>359250</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>36,31%</t>
+          <t>36,13%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>43,07%</t>
+          <t>43,05%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>196394</t>
+          <t>197450</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>229699</t>
+          <t>229963</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>61,95%</t>
+          <t>62,28%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>72,45%</t>
+          <t>72,54%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>265020</t>
+          <t>265236</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>312690</t>
+          <t>312222</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>51,22%</t>
+          <t>51,26%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>60,43%</t>
+          <t>60,34%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>475084</t>
+          <t>475206</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>531479</t>
+          <t>532981</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>56,93%</t>
+          <t>56,95%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>63,69%</t>
+          <t>63,87%</t>
         </is>
       </c>
     </row>
@@ -2428,7 +2428,7 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -2448,12 +2448,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>114289</t>
+          <t>115295</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>147847</t>
+          <t>148728</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2463,12 +2463,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>39,16%</t>
+          <t>39,5%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>50,66%</t>
+          <t>50,96%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>338656</t>
+          <t>335587</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>395735</t>
+          <t>395983</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2498,12 +2498,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>30,11%</t>
+          <t>29,83%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>35,18%</t>
+          <t>35,2%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>466027</t>
+          <t>461973</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>539178</t>
+          <t>532383</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2533,12 +2533,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>32,89%</t>
+          <t>32,61%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>38,06%</t>
+          <t>37,58%</t>
         </is>
       </c>
     </row>
@@ -2561,12 +2561,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>144018</t>
+          <t>143137</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>177576</t>
+          <t>176570</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2576,12 +2576,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>49,34%</t>
+          <t>49,04%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>60,84%</t>
+          <t>60,5%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>729168</t>
+          <t>728920</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>786247</t>
+          <t>789316</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2611,12 +2611,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>64,82%</t>
+          <t>64,8%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>69,89%</t>
+          <t>70,17%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>877590</t>
+          <t>884385</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>950741</t>
+          <t>954795</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2646,12 +2646,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>61,94%</t>
+          <t>62,42%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>67,11%</t>
+          <t>67,39%</t>
         </is>
       </c>
     </row>
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>821569</t>
+          <t>818995</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>918171</t>
+          <t>924790</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2806,12 +2806,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>26,98%</t>
+          <t>26,89%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>30,15%</t>
+          <t>30,37%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>1093542</t>
+          <t>1091966</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>1198857</t>
+          <t>1199766</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2841,12 +2841,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>35,37%</t>
+          <t>35,32%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>38,78%</t>
+          <t>38,81%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1948832</t>
+          <t>1942513</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>2095516</t>
+          <t>2092189</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>31,76%</t>
+          <t>31,65%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>34,15%</t>
+          <t>34,09%</t>
         </is>
       </c>
     </row>
@@ -2904,12 +2904,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>2127342</t>
+          <t>2120723</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>2223944</t>
+          <t>2226518</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>69,85%</t>
+          <t>69,63%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>73,02%</t>
+          <t>73,11%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>1892457</t>
+          <t>1891548</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>1997772</t>
+          <t>1999348</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,12 +2954,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>61,22%</t>
+          <t>61,19%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>64,63%</t>
+          <t>64,68%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>4041310</t>
+          <t>4044637</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>4187994</t>
+          <t>4194313</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2989,12 +2989,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>65,85%</t>
+          <t>65,91%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>68,24%</t>
+          <t>68,35%</t>
         </is>
       </c>
     </row>
@@ -3368,12 +3368,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>96449</t>
+          <t>98635</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>137144</t>
+          <t>137868</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3383,12 +3383,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>23,93%</t>
+          <t>24,47%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>34,02%</t>
+          <t>34,2%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3403,12 +3403,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>76942</t>
+          <t>77068</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>112106</t>
+          <t>109872</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3418,12 +3418,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>26,22%</t>
+          <t>26,26%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>38,2%</t>
+          <t>37,44%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3438,12 +3438,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>184089</t>
+          <t>183759</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>234527</t>
+          <t>233826</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3453,12 +3453,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>26,43%</t>
+          <t>26,38%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>33,67%</t>
+          <t>33,57%</t>
         </is>
       </c>
     </row>
@@ -3481,12 +3481,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>265979</t>
+          <t>265255</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>306674</t>
+          <t>304488</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3496,12 +3496,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>65,98%</t>
+          <t>65,8%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>76,07%</t>
+          <t>75,53%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3516,12 +3516,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>181363</t>
+          <t>183597</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>216527</t>
+          <t>216401</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3531,12 +3531,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>61,8%</t>
+          <t>62,56%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>73,78%</t>
+          <t>73,74%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3551,12 +3551,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>462065</t>
+          <t>462766</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>512503</t>
+          <t>512833</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3566,12 +3566,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>66,33%</t>
+          <t>66,43%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>73,57%</t>
+          <t>73,62%</t>
         </is>
       </c>
     </row>
@@ -3711,12 +3711,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>87037</t>
+          <t>89921</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>126439</t>
+          <t>126465</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3726,7 +3726,7 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>21,61%</t>
+          <t>22,33%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
@@ -3746,12 +3746,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>87743</t>
+          <t>85559</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>122145</t>
+          <t>123238</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3761,12 +3761,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>27,15%</t>
+          <t>26,48%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>37,8%</t>
+          <t>38,14%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3781,12 +3781,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>185074</t>
+          <t>185054</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>238326</t>
+          <t>236596</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3796,12 +3796,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>25,5%</t>
+          <t>25,49%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>32,83%</t>
+          <t>32,59%</t>
         </is>
       </c>
     </row>
@@ -3824,12 +3824,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>276294</t>
+          <t>276268</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>315696</t>
+          <t>312812</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3844,7 +3844,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>78,39%</t>
+          <t>77,67%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3859,12 +3859,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>200988</t>
+          <t>199895</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>235390</t>
+          <t>237574</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3874,12 +3874,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>62,2%</t>
+          <t>61,86%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>72,85%</t>
+          <t>73,52%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3894,12 +3894,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>487541</t>
+          <t>489271</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>540793</t>
+          <t>540813</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3909,12 +3909,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>67,17%</t>
+          <t>67,41%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>74,5%</t>
+          <t>74,51%</t>
         </is>
       </c>
     </row>
@@ -4054,12 +4054,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>182659</t>
+          <t>184090</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>228832</t>
+          <t>229744</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4069,12 +4069,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>30,06%</t>
+          <t>30,29%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>37,65%</t>
+          <t>37,8%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4089,12 +4089,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>89731</t>
+          <t>86947</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>120728</t>
+          <t>119736</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4104,12 +4104,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>37,32%</t>
+          <t>36,16%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>50,21%</t>
+          <t>49,8%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4124,12 +4124,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>283917</t>
+          <t>282248</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>340303</t>
+          <t>339294</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4139,12 +4139,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>33,47%</t>
+          <t>33,28%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>40,12%</t>
+          <t>40,0%</t>
         </is>
       </c>
     </row>
@@ -4167,12 +4167,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>378905</t>
+          <t>377993</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>425078</t>
+          <t>423647</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4182,12 +4182,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>62,35%</t>
+          <t>62,2%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>69,94%</t>
+          <t>69,71%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4202,12 +4202,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>119720</t>
+          <t>120712</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>150717</t>
+          <t>153501</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4217,12 +4217,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>49,79%</t>
+          <t>50,2%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>62,68%</t>
+          <t>63,84%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4237,12 +4237,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>507882</t>
+          <t>508891</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>564268</t>
+          <t>565937</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4252,12 +4252,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>59,88%</t>
+          <t>60,0%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>66,53%</t>
+          <t>66,72%</t>
         </is>
       </c>
     </row>
@@ -4397,12 +4397,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>335317</t>
+          <t>337823</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>400254</t>
+          <t>404934</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4412,12 +4412,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>30,33%</t>
+          <t>30,56%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>36,21%</t>
+          <t>36,63%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4432,12 +4432,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>286004</t>
+          <t>288272</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>339583</t>
+          <t>341554</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4447,12 +4447,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>38,38%</t>
+          <t>38,68%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>45,56%</t>
+          <t>45,83%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4467,12 +4467,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>634926</t>
+          <t>640636</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>722785</t>
+          <t>728758</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4482,12 +4482,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>34,31%</t>
+          <t>34,62%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>39,06%</t>
+          <t>39,38%</t>
         </is>
       </c>
     </row>
@@ -4510,12 +4510,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>705137</t>
+          <t>700457</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>770074</t>
+          <t>767568</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4525,12 +4525,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>63,79%</t>
+          <t>63,37%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>69,67%</t>
+          <t>69,44%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4545,12 +4545,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>405691</t>
+          <t>403720</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>459270</t>
+          <t>457002</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>54,44%</t>
+          <t>54,17%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>61,62%</t>
+          <t>61,32%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4580,12 +4580,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1127880</t>
+          <t>1121907</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1215739</t>
+          <t>1210029</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4595,12 +4595,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>60,94%</t>
+          <t>60,62%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>65,69%</t>
+          <t>65,38%</t>
         </is>
       </c>
     </row>
@@ -4740,12 +4740,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>141882</t>
+          <t>141251</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>184975</t>
+          <t>182966</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4755,12 +4755,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>28,8%</t>
+          <t>28,68%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>37,55%</t>
+          <t>37,15%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4775,12 +4775,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>271588</t>
+          <t>269452</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>325471</t>
+          <t>322988</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4790,12 +4790,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>37,44%</t>
+          <t>37,15%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>44,87%</t>
+          <t>44,53%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>425920</t>
+          <t>429403</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>494809</t>
+          <t>496038</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4825,12 +4825,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>34,97%</t>
+          <t>35,26%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>40,63%</t>
+          <t>40,73%</t>
         </is>
       </c>
     </row>
@@ -4853,12 +4853,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>307588</t>
+          <t>309597</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>350681</t>
+          <t>351312</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4868,12 +4868,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>62,45%</t>
+          <t>62,85%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>71,2%</t>
+          <t>71,32%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4888,12 +4888,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>399926</t>
+          <t>402409</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>453809</t>
+          <t>455945</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4903,12 +4903,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>55,13%</t>
+          <t>55,47%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>62,56%</t>
+          <t>62,85%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4923,12 +4923,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>723150</t>
+          <t>721921</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>792039</t>
+          <t>788556</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4938,12 +4938,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>59,37%</t>
+          <t>59,27%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>65,03%</t>
+          <t>64,74%</t>
         </is>
       </c>
     </row>
@@ -5063,7 +5063,7 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -5083,12 +5083,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>96917</t>
+          <t>97906</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>128142</t>
+          <t>130263</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5098,12 +5098,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>36,7%</t>
+          <t>37,08%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>48,53%</t>
+          <t>49,33%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5118,12 +5118,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>358209</t>
+          <t>359588</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>422047</t>
+          <t>422943</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5133,12 +5133,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>34,88%</t>
+          <t>35,02%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>41,1%</t>
+          <t>41,19%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>464156</t>
+          <t>468960</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>534509</t>
+          <t>537904</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5168,12 +5168,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>35,95%</t>
+          <t>36,33%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>41,4%</t>
+          <t>41,67%</t>
         </is>
       </c>
     </row>
@@ -5196,12 +5196,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>135919</t>
+          <t>133798</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>167144</t>
+          <t>166155</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5211,12 +5211,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>51,47%</t>
+          <t>50,67%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>63,3%</t>
+          <t>62,92%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5231,12 +5231,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>604841</t>
+          <t>603945</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>668679</t>
+          <t>667300</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5246,12 +5246,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>58,9%</t>
+          <t>58,81%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>65,12%</t>
+          <t>64,98%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5266,12 +5266,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>756440</t>
+          <t>753045</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>826793</t>
+          <t>821989</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5281,12 +5281,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>58,6%</t>
+          <t>58,33%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>64,05%</t>
+          <t>63,67%</t>
         </is>
       </c>
     </row>
@@ -5426,12 +5426,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>1021170</t>
+          <t>1020251</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>1133224</t>
+          <t>1133118</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5441,12 +5441,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>31,17%</t>
+          <t>31,15%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>34,6%</t>
+          <t>34,59%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5461,12 +5461,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>1239312</t>
+          <t>1240763</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>1354725</t>
+          <t>1354744</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5476,7 +5476,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>36,94%</t>
+          <t>36,99%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>2289821</t>
+          <t>2298464</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>2457704</t>
+          <t>2470917</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>34,54%</t>
+          <t>34,67%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>37,07%</t>
+          <t>37,27%</t>
         </is>
       </c>
     </row>
@@ -5539,12 +5539,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>2142384</t>
+          <t>2142490</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>2254438</t>
+          <t>2255357</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5554,12 +5554,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>65,4%</t>
+          <t>65,41%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>68,83%</t>
+          <t>68,85%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5574,12 +5574,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>1999883</t>
+          <t>1999864</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>2115296</t>
+          <t>2113845</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5594,7 +5594,7 @@
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>63,06%</t>
+          <t>63,01%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5609,12 +5609,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>4172513</t>
+          <t>4159300</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>4340396</t>
+          <t>4331753</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5624,12 +5624,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>62,93%</t>
+          <t>62,73%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>65,46%</t>
+          <t>65,33%</t>
         </is>
       </c>
     </row>
@@ -6003,12 +6003,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>56781</t>
+          <t>56981</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>88310</t>
+          <t>87325</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6018,12 +6018,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>14,91%</t>
+          <t>14,96%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>23,19%</t>
+          <t>22,93%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6038,12 +6038,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>60059</t>
+          <t>59277</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>89100</t>
+          <t>89173</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6053,12 +6053,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>18,92%</t>
+          <t>18,67%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>28,07%</t>
+          <t>28,09%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6073,12 +6073,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>123604</t>
+          <t>124819</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>168563</t>
+          <t>166202</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6088,12 +6088,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>17,7%</t>
+          <t>17,88%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>24,14%</t>
+          <t>23,8%</t>
         </is>
       </c>
     </row>
@@ -6116,12 +6116,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>292453</t>
+          <t>293438</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>323982</t>
+          <t>323782</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6131,12 +6131,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>76,81%</t>
+          <t>77,07%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>85,09%</t>
+          <t>85,04%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6151,12 +6151,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>228348</t>
+          <t>228275</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>257389</t>
+          <t>258171</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6166,12 +6166,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>71,93%</t>
+          <t>71,91%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>81,08%</t>
+          <t>81,33%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6186,12 +6186,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>529647</t>
+          <t>532008</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>574606</t>
+          <t>573391</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6201,12 +6201,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>75,86%</t>
+          <t>76,2%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>82,3%</t>
+          <t>82,12%</t>
         </is>
       </c>
     </row>
@@ -6346,12 +6346,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>56292</t>
+          <t>58376</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>86825</t>
+          <t>87369</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -6361,12 +6361,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>15,84%</t>
+          <t>16,43%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>24,44%</t>
+          <t>24,59%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6381,12 +6381,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>64205</t>
+          <t>63280</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>97713</t>
+          <t>95045</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6396,12 +6396,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>18,77%</t>
+          <t>18,5%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>28,56%</t>
+          <t>27,79%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6416,12 +6416,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>130252</t>
+          <t>131348</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>172925</t>
+          <t>172606</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -6431,12 +6431,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>18,68%</t>
+          <t>18,84%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>24,8%</t>
+          <t>24,75%</t>
         </is>
       </c>
     </row>
@@ -6459,12 +6459,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>268460</t>
+          <t>267916</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>298993</t>
+          <t>296909</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -6474,12 +6474,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>75,56%</t>
+          <t>75,41%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>84,16%</t>
+          <t>83,57%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6494,12 +6494,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>244360</t>
+          <t>247028</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>277868</t>
+          <t>278793</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -6509,12 +6509,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>71,44%</t>
+          <t>72,21%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>81,23%</t>
+          <t>81,5%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6529,12 +6529,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>524433</t>
+          <t>524752</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>567106</t>
+          <t>566010</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -6544,12 +6544,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>75,2%</t>
+          <t>75,25%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>81,32%</t>
+          <t>81,16%</t>
         </is>
       </c>
     </row>
@@ -6689,12 +6689,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>106687</t>
+          <t>106438</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>146391</t>
+          <t>148234</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6704,12 +6704,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>21,87%</t>
+          <t>21,82%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>30,01%</t>
+          <t>30,39%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6724,12 +6724,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>23872</t>
+          <t>23015</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>44788</t>
+          <t>44409</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6739,12 +6739,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>15,59%</t>
+          <t>15,03%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>29,24%</t>
+          <t>28,99%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6759,12 +6759,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>135074</t>
+          <t>137921</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>181607</t>
+          <t>183336</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6774,12 +6774,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>21,07%</t>
+          <t>21,52%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>28,34%</t>
+          <t>28,6%</t>
         </is>
       </c>
     </row>
@@ -6802,12 +6802,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>341375</t>
+          <t>339532</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>381079</t>
+          <t>381328</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -6817,12 +6817,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>69,99%</t>
+          <t>69,61%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>78,13%</t>
+          <t>78,18%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6837,12 +6837,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>108373</t>
+          <t>108752</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>129289</t>
+          <t>130146</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -6852,12 +6852,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>70,76%</t>
+          <t>71,01%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>84,41%</t>
+          <t>84,97%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6872,12 +6872,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>459320</t>
+          <t>457591</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>505853</t>
+          <t>503006</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6887,12 +6887,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>71,66%</t>
+          <t>71,4%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>78,93%</t>
+          <t>78,48%</t>
         </is>
       </c>
     </row>
@@ -7032,12 +7032,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>263681</t>
+          <t>264382</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>321480</t>
+          <t>321158</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7047,12 +7047,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>24,45%</t>
+          <t>24,52%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>29,82%</t>
+          <t>29,79%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>206654</t>
+          <t>206018</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>258990</t>
+          <t>259616</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7082,12 +7082,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>26,82%</t>
+          <t>26,74%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>33,62%</t>
+          <t>33,7%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7102,12 +7102,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>481807</t>
+          <t>483267</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>560144</t>
+          <t>562761</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7117,12 +7117,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>26,06%</t>
+          <t>26,14%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>30,3%</t>
+          <t>30,44%</t>
         </is>
       </c>
     </row>
@@ -7145,12 +7145,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>756757</t>
+          <t>757079</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>814556</t>
+          <t>813855</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7160,12 +7160,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>70,18%</t>
+          <t>70,21%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>75,55%</t>
+          <t>75,48%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7180,12 +7180,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>511456</t>
+          <t>510830</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>563792</t>
+          <t>564428</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7195,12 +7195,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>66,38%</t>
+          <t>66,3%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>73,18%</t>
+          <t>73,26%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7215,12 +7215,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1288539</t>
+          <t>1285922</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1366876</t>
+          <t>1365416</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7230,12 +7230,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>69,7%</t>
+          <t>69,56%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>73,94%</t>
+          <t>73,86%</t>
         </is>
       </c>
     </row>
@@ -7375,12 +7375,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>116986</t>
+          <t>115314</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>156103</t>
+          <t>158025</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7390,12 +7390,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>20,91%</t>
+          <t>20,62%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>27,91%</t>
+          <t>28,25%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7410,12 +7410,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>186533</t>
+          <t>183596</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>232979</t>
+          <t>231671</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7425,12 +7425,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>27,15%</t>
+          <t>26,72%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>33,91%</t>
+          <t>33,72%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -7445,12 +7445,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>312863</t>
+          <t>313486</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>375112</t>
+          <t>378306</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -7460,12 +7460,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>25,1%</t>
+          <t>25,15%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>30,1%</t>
+          <t>30,35%</t>
         </is>
       </c>
     </row>
@@ -7488,12 +7488,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>403261</t>
+          <t>401339</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>442378</t>
+          <t>444050</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -7503,12 +7503,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>72,09%</t>
+          <t>71,75%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>79,09%</t>
+          <t>79,38%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -7523,12 +7523,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>454028</t>
+          <t>455336</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>500474</t>
+          <t>503411</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -7538,12 +7538,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>66,09%</t>
+          <t>66,28%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>72,85%</t>
+          <t>73,28%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -7558,12 +7558,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>871259</t>
+          <t>868065</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>933508</t>
+          <t>932885</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -7573,12 +7573,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>69,9%</t>
+          <t>69,65%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>74,9%</t>
+          <t>74,85%</t>
         </is>
       </c>
     </row>
@@ -7698,7 +7698,7 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -7718,12 +7718,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>81810</t>
+          <t>81576</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>113818</t>
+          <t>117094</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -7733,12 +7733,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>29,12%</t>
+          <t>29,04%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>40,52%</t>
+          <t>41,69%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -7753,12 +7753,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>217467</t>
+          <t>220897</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>275182</t>
+          <t>273708</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -7768,12 +7768,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>21,74%</t>
+          <t>22,08%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>27,51%</t>
+          <t>27,36%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -7788,12 +7788,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>311666</t>
+          <t>314440</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>378977</t>
+          <t>379412</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -7803,12 +7803,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>24,33%</t>
+          <t>24,54%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>29,58%</t>
+          <t>29,61%</t>
         </is>
       </c>
     </row>
@@ -7831,12 +7831,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>167081</t>
+          <t>163805</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>199089</t>
+          <t>199323</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -7846,12 +7846,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>59,48%</t>
+          <t>58,31%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>70,88%</t>
+          <t>70,96%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -7866,12 +7866,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>725074</t>
+          <t>726548</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>782789</t>
+          <t>779359</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -7881,12 +7881,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>72,49%</t>
+          <t>72,64%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>78,26%</t>
+          <t>77,92%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -7901,12 +7901,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>902178</t>
+          <t>901743</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>969489</t>
+          <t>966715</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -7916,12 +7916,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>70,42%</t>
+          <t>70,39%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>75,67%</t>
+          <t>75,46%</t>
         </is>
       </c>
     </row>
@@ -8061,12 +8061,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>743845</t>
+          <t>743233</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>839472</t>
+          <t>836363</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8076,12 +8076,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>23,67%</t>
+          <t>23,65%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>26,72%</t>
+          <t>26,62%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8096,12 +8096,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>821065</t>
+          <t>823496</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>925357</t>
+          <t>926852</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8111,12 +8111,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>25,11%</t>
+          <t>25,18%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>28,29%</t>
+          <t>28,34%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8131,12 +8131,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1587033</t>
+          <t>1597086</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1732832</t>
+          <t>1738674</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8146,12 +8146,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>24,75%</t>
+          <t>24,91%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>27,02%</t>
+          <t>27,11%</t>
         </is>
       </c>
     </row>
@@ -8174,12 +8174,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>2302841</t>
+          <t>2305950</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>2398468</t>
+          <t>2399080</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -8189,12 +8189,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>73,28%</t>
+          <t>73,38%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>76,33%</t>
+          <t>76,35%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -8209,12 +8209,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>2345034</t>
+          <t>2343539</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>2449326</t>
+          <t>2446895</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -8224,12 +8224,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>71,71%</t>
+          <t>71,66%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>74,89%</t>
+          <t>74,82%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -8244,12 +8244,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>4679872</t>
+          <t>4674030</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>4825671</t>
+          <t>4815618</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8259,12 +8259,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>72,98%</t>
+          <t>72,89%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>75,25%</t>
+          <t>75,09%</t>
         </is>
       </c>
     </row>
@@ -8633,32 +8633,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>41987</t>
+          <t>46012</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>29814</t>
+          <t>34049</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>57670</t>
+          <t>62337</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>9,03%</t>
+          <t>9,12%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>6,41%</t>
+          <t>6,75%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>12,4%</t>
+          <t>12,35%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -8668,32 +8668,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>41540</t>
+          <t>45553</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>32341</t>
+          <t>34630</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>54126</t>
+          <t>58993</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>10,03%</t>
+          <t>10,11%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>7,81%</t>
+          <t>7,68%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>13,07%</t>
+          <t>13,09%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -8703,27 +8703,27 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>83527</t>
+          <t>91565</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>67714</t>
+          <t>74754</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>102757</t>
+          <t>111681</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>9,5%</t>
+          <t>9,58%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>7,7%</t>
+          <t>7,82%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
@@ -8746,32 +8746,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>422961</t>
+          <t>458689</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>407278</t>
+          <t>442364</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>435134</t>
+          <t>470652</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>90,97%</t>
+          <t>90,88%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>87,6%</t>
+          <t>87,65%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>93,59%</t>
+          <t>93,25%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -8781,32 +8781,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>372562</t>
+          <t>405115</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>359976</t>
+          <t>391675</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>381761</t>
+          <t>416038</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>89,97%</t>
+          <t>89,89%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>86,93%</t>
+          <t>86,91%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>92,19%</t>
+          <t>92,32%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -8816,22 +8816,22 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>795524</t>
+          <t>863804</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>776294</t>
+          <t>843688</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>811337</t>
+          <t>880615</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>90,5%</t>
+          <t>90,42%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
@@ -8841,7 +8841,7 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>92,3%</t>
+          <t>92,18%</t>
         </is>
       </c>
     </row>
@@ -8859,17 +8859,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>464948</t>
+          <t>504701</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>464948</t>
+          <t>504701</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>464948</t>
+          <t>504701</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -8894,17 +8894,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>414102</t>
+          <t>450668</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>414102</t>
+          <t>450668</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>414102</t>
+          <t>450668</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -8929,17 +8929,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>879051</t>
+          <t>955369</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>879051</t>
+          <t>955369</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>879051</t>
+          <t>955369</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -8976,32 +8976,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>37603</t>
+          <t>35721</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>25978</t>
+          <t>24422</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>58870</t>
+          <t>51204</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>9,01%</t>
+          <t>8,03%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>6,23%</t>
+          <t>5,49%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>14,11%</t>
+          <t>11,5%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -9011,32 +9011,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>45712</t>
+          <t>50476</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>34807</t>
+          <t>38962</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>59064</t>
+          <t>63430</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>12,73%</t>
+          <t>12,72%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>9,69%</t>
+          <t>9,82%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>16,44%</t>
+          <t>15,99%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -9046,32 +9046,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>83316</t>
+          <t>86198</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>66085</t>
+          <t>68882</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>104048</t>
+          <t>106939</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>10,73%</t>
+          <t>10,24%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>8,51%</t>
+          <t>8,18%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>13,4%</t>
+          <t>12,7%</t>
         </is>
       </c>
     </row>
@@ -9089,32 +9089,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>379565</t>
+          <t>409370</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>358298</t>
+          <t>393887</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>391190</t>
+          <t>420669</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>90,99%</t>
+          <t>91,97%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>85,89%</t>
+          <t>88,5%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>93,77%</t>
+          <t>94,51%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -9124,32 +9124,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>313516</t>
+          <t>346205</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>300164</t>
+          <t>333251</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>324421</t>
+          <t>357719</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>87,27%</t>
+          <t>87,28%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>83,56%</t>
+          <t>84,01%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>90,31%</t>
+          <t>90,18%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -9159,32 +9159,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>693081</t>
+          <t>755574</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>672349</t>
+          <t>734833</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>710312</t>
+          <t>772890</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>89,27%</t>
+          <t>89,76%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>86,6%</t>
+          <t>87,3%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>91,49%</t>
+          <t>91,82%</t>
         </is>
       </c>
     </row>
@@ -9202,17 +9202,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>417168</t>
+          <t>445091</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>417168</t>
+          <t>445091</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>417168</t>
+          <t>445091</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -9237,17 +9237,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>359228</t>
+          <t>396681</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>359228</t>
+          <t>396681</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>359228</t>
+          <t>396681</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -9272,17 +9272,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>776397</t>
+          <t>841772</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>776397</t>
+          <t>841772</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>776397</t>
+          <t>841772</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -9319,32 +9319,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>276948</t>
+          <t>37752</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>47633</t>
+          <t>27836</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>493456</t>
+          <t>52041</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>43,98%</t>
+          <t>8,76%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>7,56%</t>
+          <t>6,46%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>78,35%</t>
+          <t>12,08%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -9354,32 +9354,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>12833</t>
+          <t>14285</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>7973</t>
+          <t>9054</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>19158</t>
+          <t>21889</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>8,62%</t>
+          <t>8,53%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>5,36%</t>
+          <t>5,41%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>12,87%</t>
+          <t>13,07%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -9389,32 +9389,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>289781</t>
+          <t>52038</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>60505</t>
+          <t>39773</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>579342</t>
+          <t>66182</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>37,22%</t>
+          <t>8,7%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>7,77%</t>
+          <t>6,65%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>74,41%</t>
+          <t>11,06%</t>
         </is>
       </c>
     </row>
@@ -9432,32 +9432,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>352823</t>
+          <t>393149</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>136315</t>
+          <t>378860</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>582138</t>
+          <t>403065</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>56,02%</t>
+          <t>91,24%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>21,65%</t>
+          <t>87,92%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>92,44%</t>
+          <t>93,54%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -9467,32 +9467,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>135998</t>
+          <t>153215</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>129673</t>
+          <t>145611</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>140858</t>
+          <t>158446</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>91,38%</t>
+          <t>91,47%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>87,13%</t>
+          <t>86,93%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>94,64%</t>
+          <t>94,59%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -9502,32 +9502,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>488822</t>
+          <t>546362</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>199261</t>
+          <t>532218</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>718098</t>
+          <t>558627</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>62,78%</t>
+          <t>91,3%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>25,59%</t>
+          <t>88,94%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>92,23%</t>
+          <t>93,35%</t>
         </is>
       </c>
     </row>
@@ -9545,17 +9545,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>629771</t>
+          <t>430901</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>629771</t>
+          <t>430901</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>629771</t>
+          <t>430901</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -9580,17 +9580,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>148831</t>
+          <t>167500</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>148831</t>
+          <t>167500</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>148831</t>
+          <t>167500</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -9615,17 +9615,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>778603</t>
+          <t>598400</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>778603</t>
+          <t>598400</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>778603</t>
+          <t>598400</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -9662,32 +9662,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>123969</t>
+          <t>132901</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>101631</t>
+          <t>110345</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>151686</t>
+          <t>160696</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>13,36%</t>
+          <t>13,11%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>10,95%</t>
+          <t>10,89%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>16,35%</t>
+          <t>15,85%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -9697,32 +9697,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>131256</t>
+          <t>141192</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>59946</t>
+          <t>124322</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>176237</t>
+          <t>161362</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>14,21%</t>
+          <t>17,66%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>6,49%</t>
+          <t>15,55%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>19,08%</t>
+          <t>20,19%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -9732,32 +9732,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>255225</t>
+          <t>274093</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>168884</t>
+          <t>242548</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>302248</t>
+          <t>313202</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>13,79%</t>
+          <t>15,12%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>9,12%</t>
+          <t>13,38%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>16,33%</t>
+          <t>17,28%</t>
         </is>
       </c>
     </row>
@@ -9775,32 +9775,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>803797</t>
+          <t>880653</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>776080</t>
+          <t>852858</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>826135</t>
+          <t>903209</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>86,64%</t>
+          <t>86,89%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>83,65%</t>
+          <t>84,15%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>89,05%</t>
+          <t>89,11%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -9810,32 +9810,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>792368</t>
+          <t>658167</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>747387</t>
+          <t>637997</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>863678</t>
+          <t>675037</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>85,79%</t>
+          <t>82,34%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>80,92%</t>
+          <t>79,81%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>93,51%</t>
+          <t>84,45%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -9845,32 +9845,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>1596165</t>
+          <t>1538820</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1549142</t>
+          <t>1499711</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1682506</t>
+          <t>1570365</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>86,21%</t>
+          <t>84,88%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>83,67%</t>
+          <t>82,72%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>90,88%</t>
+          <t>86,62%</t>
         </is>
       </c>
     </row>
@@ -9888,17 +9888,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>927766</t>
+          <t>1013554</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>927766</t>
+          <t>1013554</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>927766</t>
+          <t>1013554</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -9923,17 +9923,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>923624</t>
+          <t>799359</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>923624</t>
+          <t>799359</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>923624</t>
+          <t>799359</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -9958,17 +9958,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>1851390</t>
+          <t>1812913</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>1851390</t>
+          <t>1812913</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>1851390</t>
+          <t>1812913</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -10005,32 +10005,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>58518</t>
+          <t>69600</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>44162</t>
+          <t>54065</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>74531</t>
+          <t>88014</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>13,87%</t>
+          <t>14,11%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>10,47%</t>
+          <t>10,96%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>17,67%</t>
+          <t>17,85%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -10040,32 +10040,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>106382</t>
+          <t>115636</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>76746</t>
+          <t>99935</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>126755</t>
+          <t>133747</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>13,79%</t>
+          <t>15,28%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>9,94%</t>
+          <t>13,21%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>16,43%</t>
+          <t>17,68%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -10075,32 +10075,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>164900</t>
+          <t>185236</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>133535</t>
+          <t>163250</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>191929</t>
+          <t>211743</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>13,82%</t>
+          <t>14,82%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>11,19%</t>
+          <t>13,06%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>16,08%</t>
+          <t>16,94%</t>
         </is>
       </c>
     </row>
@@ -10118,32 +10118,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>363319</t>
+          <t>423495</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>347306</t>
+          <t>405081</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>377675</t>
+          <t>439030</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>86,13%</t>
+          <t>85,89%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>82,33%</t>
+          <t>82,15%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>89,53%</t>
+          <t>89,04%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -10153,32 +10153,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>665328</t>
+          <t>640915</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>644955</t>
+          <t>622804</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>694964</t>
+          <t>656616</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>86,21%</t>
+          <t>84,72%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>83,57%</t>
+          <t>82,32%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>90,06%</t>
+          <t>86,79%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -10188,32 +10188,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>1028647</t>
+          <t>1064410</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1001618</t>
+          <t>1037903</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1060012</t>
+          <t>1086396</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>86,18%</t>
+          <t>85,18%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>83,92%</t>
+          <t>83,06%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>88,81%</t>
+          <t>86,94%</t>
         </is>
       </c>
     </row>
@@ -10231,17 +10231,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>421837</t>
+          <t>493095</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>421837</t>
+          <t>493095</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>421837</t>
+          <t>493095</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -10266,17 +10266,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>771710</t>
+          <t>756551</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>771710</t>
+          <t>756551</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>771710</t>
+          <t>756551</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -10301,17 +10301,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>1193547</t>
+          <t>1249646</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1193547</t>
+          <t>1249646</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1193547</t>
+          <t>1249646</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -10333,7 +10333,7 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -10348,32 +10348,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>34736</t>
+          <t>32366</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>19582</t>
+          <t>18146</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>57138</t>
+          <t>53623</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>15,24%</t>
+          <t>14,32%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>8,59%</t>
+          <t>8,03%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>25,08%</t>
+          <t>23,73%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -10383,32 +10383,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>82990</t>
+          <t>86010</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>65627</t>
+          <t>68567</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>107036</t>
+          <t>108742</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>12,41%</t>
+          <t>11,54%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>9,81%</t>
+          <t>9,2%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>16,0%</t>
+          <t>14,58%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -10418,32 +10418,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>117726</t>
+          <t>118376</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>92752</t>
+          <t>95902</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>144375</t>
+          <t>144960</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>13,13%</t>
+          <t>12,18%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>10,34%</t>
+          <t>9,87%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>16,1%</t>
+          <t>14,92%</t>
         </is>
       </c>
     </row>
@@ -10461,32 +10461,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>193123</t>
+          <t>193584</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>170721</t>
+          <t>172327</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>208277</t>
+          <t>207804</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>84,76%</t>
+          <t>85,68%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>74,92%</t>
+          <t>76,27%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>91,41%</t>
+          <t>91,97%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -10496,32 +10496,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>585835</t>
+          <t>659624</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>561789</t>
+          <t>636892</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>603198</t>
+          <t>677067</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>87,59%</t>
+          <t>88,46%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>84,0%</t>
+          <t>85,42%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>90,19%</t>
+          <t>90,8%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -10531,32 +10531,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>778958</t>
+          <t>853208</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>752309</t>
+          <t>826624</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>803932</t>
+          <t>875682</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>86,87%</t>
+          <t>87,82%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>83,9%</t>
+          <t>85,08%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>89,66%</t>
+          <t>90,13%</t>
         </is>
       </c>
     </row>
@@ -10574,17 +10574,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>227859</t>
+          <t>225950</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>227859</t>
+          <t>225950</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>227859</t>
+          <t>225950</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -10609,17 +10609,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>668825</t>
+          <t>745634</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>668825</t>
+          <t>745634</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>668825</t>
+          <t>745634</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -10644,17 +10644,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>896684</t>
+          <t>971584</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>896684</t>
+          <t>971584</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>896684</t>
+          <t>971584</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -10691,32 +10691,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>573762</t>
+          <t>354352</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>344351</t>
+          <t>312528</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>1232840</t>
+          <t>397242</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>18,57%</t>
+          <t>11,38%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>11,15%</t>
+          <t>10,04%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>39,91%</t>
+          <t>12,76%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -10726,32 +10726,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>420714</t>
+          <t>453153</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>343902</t>
+          <t>413856</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>470313</t>
+          <t>489416</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>12,8%</t>
+          <t>13,66%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>10,46%</t>
+          <t>12,48%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>14,31%</t>
+          <t>14,76%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -10761,32 +10761,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>994475</t>
+          <t>807505</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>749560</t>
+          <t>752155</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1773213</t>
+          <t>863038</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>15,6%</t>
+          <t>12,56%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>11,76%</t>
+          <t>11,7%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>27,81%</t>
+          <t>13,42%</t>
         </is>
       </c>
     </row>
@@ -10804,32 +10804,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>2515589</t>
+          <t>2758940</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>1856511</t>
+          <t>2716050</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>2745000</t>
+          <t>2800764</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>81,43%</t>
+          <t>88,62%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>60,09%</t>
+          <t>87,24%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>88,85%</t>
+          <t>89,96%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -10839,32 +10839,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>2865607</t>
+          <t>2863240</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>2816008</t>
+          <t>2826977</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>2942419</t>
+          <t>2902537</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>87,2%</t>
+          <t>86,34%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>85,69%</t>
+          <t>85,24%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>89,54%</t>
+          <t>87,52%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -10874,32 +10874,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>5381197</t>
+          <t>5622180</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>4602459</t>
+          <t>5566647</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>5626112</t>
+          <t>5677530</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>84,4%</t>
+          <t>87,44%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>72,19%</t>
+          <t>86,58%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>88,24%</t>
+          <t>88,3%</t>
         </is>
       </c>
     </row>
@@ -10917,17 +10917,17 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>3089351</t>
+          <t>3113292</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>3089351</t>
+          <t>3113292</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>3089351</t>
+          <t>3113292</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -10952,17 +10952,17 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>3286321</t>
+          <t>3316393</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>3286321</t>
+          <t>3316393</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>3286321</t>
+          <t>3316393</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -10987,17 +10987,17 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>6375672</t>
+          <t>6429685</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>6375672</t>
+          <t>6429685</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>6375672</t>
+          <t>6429685</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
